--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.64295761337348</v>
+        <v>4.16698061217319</v>
       </c>
       <c r="D2" t="n">
-        <v>20.7515590497484</v>
+        <v>3.372128345584115</v>
       </c>
       <c r="E2" t="n">
-        <v>9.415812759850429</v>
+        <v>1.530069573475695</v>
       </c>
       <c r="F2" t="n">
-        <v>9.595281646038666</v>
+        <v>1.559233267481283</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.35364299905921</v>
+        <v>2.007466987347122</v>
       </c>
       <c r="D3" t="n">
-        <v>13.01889101453748</v>
+        <v>2.115569789862341</v>
       </c>
       <c r="E3" t="n">
-        <v>9.415812759850429</v>
+        <v>1.530069573475695</v>
       </c>
       <c r="F3" t="n">
-        <v>9.595281646038666</v>
+        <v>1.559233267481283</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.62261080437811</v>
+        <v>5.951174255711443</v>
       </c>
       <c r="D4" t="n">
-        <v>36.36859890496585</v>
+        <v>5.909897322056951</v>
       </c>
       <c r="E4" t="n">
-        <v>9.415812759850429</v>
+        <v>1.530069573475695</v>
       </c>
       <c r="F4" t="n">
-        <v>9.595281646038666</v>
+        <v>1.559233267481283</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.7612372297362</v>
+        <v>5.486201049832133</v>
       </c>
       <c r="D5" t="n">
-        <v>34.04506230896473</v>
+        <v>5.532322625206769</v>
       </c>
       <c r="E5" t="n">
-        <v>9.415812759850429</v>
+        <v>1.530069573475695</v>
       </c>
       <c r="F5" t="n">
-        <v>9.595281646038666</v>
+        <v>1.559233267481283</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
